--- a/고용증대_템플릿_샘플.xlsx
+++ b/고용증대_템플릿_샘플.xlsx
@@ -450,18 +450,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,35 +478,40 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>상시근로자</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>상시근로자제외사유</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>단시간근로자유형</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>내국인</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>수도권</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>근로계약체결일</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>퇴사년월일</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>장애인</t>
         </is>
@@ -514,21 +520,25 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>19920510</t>
+          <t>19600201</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>김민수</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>구자덕</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>임원</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Y</t>
@@ -536,11 +546,16 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>20240315</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr">
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>20071001</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -549,21 +564,25 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>19950820</t>
+          <t>19650402</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>이서연</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>구자화</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>임원</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Y</t>
@@ -571,11 +590,16 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>20250201</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr">
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>20071001</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -584,33 +608,38 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>19780115</t>
+          <t>19670530</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>박정호</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
+          <t>지춘경</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>20200601</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr">
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>20150506</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -619,25 +648,21 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>19850930</t>
+          <t>19830119</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>최영미</t>
+          <t>박건이</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>임원</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Y</t>
@@ -645,11 +670,16 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20180301</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr">
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>20160301</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -658,21 +688,25 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>19880712</t>
+          <t>19890319</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>정하늘</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>구본섭</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>친족</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Y</t>
@@ -680,50 +714,56 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>20220901</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>20160801</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>19960305</t>
+          <t>19920510</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>한소희</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>김민수</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20250301</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr">
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>20240315</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -732,21 +772,21 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>19930422</t>
+          <t>19950820</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>왕웨이</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
+          <t>이서연</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Y</t>
@@ -754,11 +794,16 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>20250115</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr">
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>20250201</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -767,21 +812,21 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>19910618</t>
+          <t>19880712</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>송지훈</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr"/>
+          <t>정하늘</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Y</t>
@@ -789,54 +834,60 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20230701</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20250831</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
+          <t>20220901</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>19870225</t>
+          <t>19960305</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>오세영</t>
+          <t>한소희</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>친족</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>20190401</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr">
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>20250301</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -845,37 +896,42 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>19760803</t>
+          <t>19910618</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>윤미래</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>송지훈</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20210301</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>20230701</t>
+        </is>
+      </c>
       <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>20250831</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -890,35 +946,40 @@
       <c r="B12" s="3" t="inlineStr"/>
       <c r="C12" s="3" t="inlineStr">
         <is>
+          <t>Y/N</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
           <t>임원/친족/기타/빈칸</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>0.5 또는 0.75</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>Y/N</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>Y/N</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>YYYYMMDD</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>YYYYMMDD(선택)</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>Y/N</t>
         </is>
@@ -965,14 +1026,14 @@
     <row r="51"/>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation sqref="C2 C3 C4 C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C35 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C46 C47 C48 C49 C50 C51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C2 C3 C4 C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C35 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C46 C47 C48 C49 C50 C51 F2 F3 F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 G2 G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51 J2 J3 J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 J38 J39 J40 J41 J42 J43 J44 J45 J46 J47 J48 J49 J50 J51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2 D3 D4 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D35 D36 D37 D38 D39 D40 D41 D42 D43 D44 D45 D46 D47 D48 D49 D50 D51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"임원,친족,기타"</formula1>
     </dataValidation>
-    <dataValidation sqref="D2 D3 D4 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D35 D36 D37 D38 D39 D40 D41 D42 D43 D44 D45 D46 D47 D48 D49 D50 D51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E2 E3 E4 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"0.5,0.75"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E2 E3 E4 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 F2 F3 F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 I2 I3 I4 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I35 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 I46 I47 I48 I49 I50 I51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
